--- a/TestData/AutomationExerFlags.xlsx
+++ b/TestData/AutomationExerFlags.xlsx
@@ -504,7 +504,7 @@
     </row>
     <row r="11">
       <c r="A11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
@@ -512,7 +512,7 @@
     </row>
     <row r="12">
       <c r="A12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
